--- a/33_GLOBAL_WL/WL_Productivity/521G - Bucket_Data v2.0 01042026.xlsx
+++ b/33_GLOBAL_WL/WL_Productivity/521G - Bucket_Data v2.0 01042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnhind-my.sharepoint.com/personal/tavinder_arora_cnhind_com/Documents/Desktop/attachmentscnh/33_GLOBAL_WL/WL_Productivity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="11_F25DC773A252ABDACC10482CE1D9707A5ADE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9C3341D-3E51-478C-9224-E2DE18C54CEB}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="11_F25DC773A252ABDACC10482CE1D9707A5ADE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4D7699D-1BFE-4687-8CA9-3B15897D6E73}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -239,10 +239,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -529,7 +525,7 @@
     <col min="16" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
